--- a/data/trans_dic/P2A_senso_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,69</t>
+          <t>0,46; 2,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,22</t>
+          <t>0,0; 0,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,53</t>
+          <t>0,58; 2,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,99</t>
+          <t>0,05; 5,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,61</t>
+          <t>0,39; 1,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,69</t>
+          <t>0,45; 1,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,28</t>
+          <t>0,05; 2,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,77</t>
+          <t>0,26; 1,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,53</t>
+          <t>0,26; 1,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,71</t>
+          <t>0,95; 4,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,83</t>
+          <t>0,3; 1,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,13</t>
+          <t>1,24; 3,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,83</t>
+          <t>0,29; 1,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,07</t>
+          <t>0,36; 2,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,3</t>
+          <t>0,4; 1,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,37</t>
+          <t>0,86; 2,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,16</t>
+          <t>0,25; 1,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,0</t>
+          <t>0,88; 3,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,03</t>
+          <t>0,16; 2,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,14</t>
+          <t>0,43; 2,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,85</t>
+          <t>0,29; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,75</t>
+          <t>0,52; 2,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,87</t>
+          <t>0,32; 1,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,06</t>
+          <t>0,83; 2,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,44</t>
+          <t>0,28; 1,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,16</t>
+          <t>0,66; 2,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,63</t>
+          <t>0,43; 1,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,12</t>
+          <t>0,82; 2,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,41</t>
+          <t>0,37; 1,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,11</t>
+          <t>0,8; 2,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,44</t>
+          <t>0,4; 2,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,18</t>
+          <t>1,22; 4,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,32</t>
+          <t>1,0; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,08</t>
+          <t>0,63; 3,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,81</t>
+          <t>1,0; 3,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,11</t>
+          <t>1,34; 3,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,17</t>
+          <t>0,31; 1,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,31</t>
+          <t>1,5; 3,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,56</t>
+          <t>0,91; 2,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,56</t>
+          <t>1,57; 3,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,22</t>
+          <t>0,85; 2,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,72</t>
+          <t>1,21; 2,81</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,66</t>
+          <t>1,86; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,69</t>
+          <t>0,95; 3,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,98</t>
+          <t>0,41; 3,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,64</t>
+          <t>2,43; 5,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,04</t>
+          <t>1,04; 4,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,6</t>
+          <t>1,4; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,95</t>
+          <t>0,19; 1,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,94</t>
+          <t>2,52; 4,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,91</t>
+          <t>1,65; 3,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,44</t>
+          <t>1,47; 3,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,87</t>
+          <t>0,42; 1,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,8</t>
+          <t>2,77; 4,89</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,32</t>
+          <t>2,71; 7,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,54</t>
+          <t>0,65; 4,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,21</t>
+          <t>0,28; 3,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,23</t>
+          <t>2,05; 5,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,47</t>
+          <t>0,55; 3,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,67</t>
+          <t>1,63; 5,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,14</t>
+          <t>0,54; 3,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 73,34</t>
+          <t>3,95; 70,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,43</t>
+          <t>1,97; 4,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,35</t>
+          <t>1,51; 4,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,54</t>
+          <t>0,67; 2,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 58,13</t>
+          <t>3,46; 59,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,53</t>
+          <t>0,86; 5,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,4</t>
+          <t>2,03; 7,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,67</t>
+          <t>0,31; 3,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,94</t>
+          <t>2,0; 5,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,42</t>
+          <t>2,34; 7,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,16</t>
+          <t>1,61; 5,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,77</t>
+          <t>1,5; 5,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,36</t>
+          <t>5,54; 9,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,46</t>
+          <t>2,22; 5,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,32</t>
+          <t>2,14; 5,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,05</t>
+          <t>1,37; 4,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,41</t>
+          <t>4,62; 7,32</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,02</t>
+          <t>1,15; 2,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,27; 2,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,47</t>
+          <t>0,68; 1,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,76</t>
+          <t>1,69; 2,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,17</t>
+          <t>1,28; 2,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,76</t>
+          <t>1,76; 2,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,47</t>
+          <t>0,75; 1,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,35</t>
+          <t>2,79; 25,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,92</t>
+          <t>1,32; 1,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,32</t>
+          <t>1,62; 2,3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,81; 1,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,39</t>
+          <t>2,47; 14,69</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8433</t>
+          <t>0; 8208</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2081; 12225</t>
+          <t>2106; 12549</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5029</t>
+          <t>0; 4882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 871</t>
+          <t>0; 701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1977; 11827</t>
+          <t>2701; 12447</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6290</t>
+          <t>0; 6658</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4485</t>
+          <t>0; 4472</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>168; 15631</t>
+          <t>169; 16204</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3805; 15491</t>
+          <t>3766; 15416</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3959; 14927</t>
+          <t>3956; 15183</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6611</t>
+          <t>0; 5846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>329; 16296</t>
+          <t>342; 14414</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1893; 13006</t>
+          <t>1881; 13182</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1817; 10526</t>
+          <t>1796; 10025</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7409</t>
+          <t>0; 6780</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4269; 24200</t>
+          <t>4010; 20951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1948; 11430</t>
+          <t>1885; 10823</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8147; 25212</t>
+          <t>7541; 24119</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1824; 10290</t>
+          <t>1653; 9872</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1180; 10607</t>
+          <t>1840; 11078</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5275; 17680</t>
+          <t>5410; 18620</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11736; 30688</t>
+          <t>11190; 30216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2828; 13430</t>
+          <t>2901; 13290</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7296; 28027</t>
+          <t>8218; 28767</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1670; 12959</t>
+          <t>1028; 13813</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2885; 14625</t>
+          <t>2929; 16461</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1941; 12370</t>
+          <t>1932; 12585</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2727; 14772</t>
+          <t>2804; 14831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2145; 12916</t>
+          <t>2178; 12920</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5805; 21753</t>
+          <t>5886; 20300</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1845; 9555</t>
+          <t>1859; 10385</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4044; 12796</t>
+          <t>3920; 13046</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5711; 21648</t>
+          <t>5669; 20606</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10932; 29493</t>
+          <t>11395; 30905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5135; 18699</t>
+          <t>4888; 17990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8611; 23777</t>
+          <t>8988; 24080</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2084; 12680</t>
+          <t>2085; 12621</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7653; 25690</t>
+          <t>7512; 26384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6933; 21440</t>
+          <t>6432; 22658</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5759; 27358</t>
+          <t>5606; 27397</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5332; 19660</t>
+          <t>5138; 17770</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8345; 25295</t>
+          <t>8233; 24428</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2988; 14061</t>
+          <t>2035; 12869</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10940; 23580</t>
+          <t>10694; 23316</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9041; 26504</t>
+          <t>9422; 26498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20216; 43838</t>
+          <t>19285; 44461</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10669; 28785</t>
+          <t>11025; 28819</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18515; 43534</t>
+          <t>19326; 45019</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7559; 21883</t>
+          <t>7182; 21273</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4130; 15825</t>
+          <t>4070; 15815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1706; 14246</t>
+          <t>1939; 14876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12882; 31675</t>
+          <t>13614; 32032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3841; 16305</t>
+          <t>4181; 16256</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6374; 20594</t>
+          <t>6279; 19712</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>968; 9673</t>
+          <t>966; 9228</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14075; 27081</t>
+          <t>13811; 27010</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13677; 30920</t>
+          <t>13052; 31532</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12587; 30220</t>
+          <t>12852; 31121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4121; 18221</t>
+          <t>4106; 19081</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30764; 53293</t>
+          <t>30744; 54229</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7778; 21407</t>
+          <t>7943; 21313</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1892; 14068</t>
+          <t>2018; 15078</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>935; 10719</t>
+          <t>949; 10362</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7377; 19270</t>
+          <t>7532; 19129</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2700; 11904</t>
+          <t>1896; 11073</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6122; 20070</t>
+          <t>5757; 19257</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2020; 11881</t>
+          <t>2035; 11375</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23424; 446147</t>
+          <t>24001; 429837</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12152; 28141</t>
+          <t>12531; 29102</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10107; 28874</t>
+          <t>10055; 27958</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4783; 18064</t>
+          <t>4780; 18217</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34401; 567629</t>
+          <t>33754; 579951</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1778; 11603</t>
+          <t>1799; 11729</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5381; 18487</t>
+          <t>5065; 18061</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>915; 9430</t>
+          <t>808; 9326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5538; 16804</t>
+          <t>5668; 16585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8927; 24773</t>
+          <t>7819; 23551</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6226; 20062</t>
+          <t>6247; 19793</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6234; 23095</t>
+          <t>6007; 22520</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23740; 39864</t>
+          <t>23592; 39644</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11638; 29690</t>
+          <t>12050; 30249</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14327; 33984</t>
+          <t>13670; 32584</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8280; 26617</t>
+          <t>9000; 28244</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32653; 52494</t>
+          <t>32763; 51840</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>38003; 66259</t>
+          <t>37661; 66661</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43387; 75044</t>
+          <t>43454; 76525</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23416; 50009</t>
+          <t>22996; 48808</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56418; 95588</t>
+          <t>58510; 99242</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>42733; 73473</t>
+          <t>43136; 72447</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>62677; 98308</t>
+          <t>62695; 97628</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27272; 52016</t>
+          <t>26546; 51329</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>103513; 941132</t>
+          <t>103528; 935404</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>86200; 127504</t>
+          <t>87814; 127417</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>112471; 161895</t>
+          <t>113441; 160581</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>54633; 90956</t>
+          <t>56035; 93225</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>176341; 1103892</t>
+          <t>177115; 1053611</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,76</t>
+          <t>0,47; 2,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,18</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,66</t>
+          <t>0,43; 2,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,17</t>
+          <t>0,45; 5,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,6</t>
+          <t>0,38; 1,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,72</t>
+          <t>0,44; 1,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,02</t>
+          <t>0,4; 3,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,79</t>
+          <t>0,26; 1,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,46</t>
+          <t>0,26; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,95</t>
+          <t>1,09; 5,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,73</t>
+          <t>0,31; 1,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,95</t>
+          <t>1,25; 4,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,75</t>
+          <t>0,3; 1,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,16</t>
+          <t>0,44; 2,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,37</t>
+          <t>0,39; 1,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,33</t>
+          <t>0,87; 2,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,15</t>
+          <t>0,24; 1,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,07</t>
+          <t>1,05; 3,68</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,16</t>
+          <t>0,26; 2,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,41</t>
+          <t>0,39; 2,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,88</t>
+          <t>0,28; 1,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,77</t>
+          <t>0,43; 2,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,87</t>
+          <t>0,43; 1,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,86</t>
+          <t>0,84; 3,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,57</t>
+          <t>0,28; 1,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,2</t>
+          <t>0,92; 2,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,55</t>
+          <t>0,46; 1,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,22</t>
+          <t>0,77; 2,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,35</t>
+          <t>0,37; 1,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,13</t>
+          <t>0,88; 2,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,43</t>
+          <t>0,4; 2,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,29</t>
+          <t>1,3; 4,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,51</t>
+          <t>1,02; 3,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,09</t>
+          <t>1,47; 3,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,45</t>
+          <t>0,98; 3,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,96</t>
+          <t>1,36; 4,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,98</t>
+          <t>0,45; 2,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,27</t>
+          <t>1,68; 3,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,56</t>
+          <t>1,0; 2,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,61</t>
+          <t>1,6; 3,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,23</t>
+          <t>0,86; 2,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,81</t>
+          <t>1,89; 3,35</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,5</t>
+          <t>1,81; 5,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,68</t>
+          <t>0,91; 3,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,11</t>
+          <t>0,41; 3,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,71</t>
+          <t>2,35; 5,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,02</t>
+          <t>1,0; 3,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,4</t>
+          <t>1,36; 4,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,86</t>
+          <t>0,19; 1,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,93</t>
+          <t>2,76; 5,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,99</t>
+          <t>1,71; 4,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,55</t>
+          <t>1,43; 3,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,96</t>
+          <t>0,4; 2,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,89</t>
+          <t>2,92; 4,85</t>
         </is>
       </c>
     </row>
@@ -1364,19 +1364,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,28</t>
+          <t>2,51; 7,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,87</t>
+          <t>0,64; 4,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,1</t>
+          <t>0,28; 3,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,2</t>
+          <t>2,13; 5,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,23</t>
+          <t>0,56; 3,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,44</t>
+          <t>1,67; 5,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,01</t>
+          <t>0,72; 3,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 70,65</t>
+          <t>3,25; 6,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,58</t>
+          <t>1,97; 4,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,21</t>
+          <t>1,49; 4,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,56</t>
+          <t>0,68; 2,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,46; 59,39</t>
+          <t>3,1; 5,19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,59</t>
+          <t>0,84; 5,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,23</t>
+          <t>2,06; 7,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,63</t>
+          <t>0,35; 3,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,87</t>
+          <t>2,05; 5,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,05</t>
+          <t>2,38; 7,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,09</t>
+          <t>1,57; 5,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,63</t>
+          <t>1,29; 5,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,31</t>
+          <t>5,85; 9,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,56</t>
+          <t>2,23; 5,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,1</t>
+          <t>2,22; 5,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,3</t>
+          <t>1,35; 4,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,32</t>
+          <t>4,66; 7,48</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,03</t>
+          <t>1,15; 2,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,23</t>
+          <t>1,25; 2,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,44</t>
+          <t>0,67; 1,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,87</t>
+          <t>1,96; 3,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,14</t>
+          <t>1,27; 2,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,74</t>
+          <t>1,72; 2,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,45</t>
+          <t>0,74; 1,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,2</t>
+          <t>2,75; 3,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,91</t>
+          <t>1,32; 1,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,3</t>
+          <t>1,6; 2,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,34</t>
+          <t>0,78; 1,31</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,69</t>
+          <t>2,55; 3,28</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>9113</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8208</t>
+          <t>0; 8417</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2106; 12549</t>
+          <t>2125; 12455</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4882</t>
+          <t>0; 5656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 701</t>
+          <t>0; 10024</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2701; 12447</t>
+          <t>2020; 12281</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6658</t>
+          <t>0; 6709</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4472</t>
+          <t>0; 4456</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>169; 16204</t>
+          <t>1648; 20765</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3766; 15416</t>
+          <t>3700; 14971</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3956; 15183</t>
+          <t>3872; 15012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5846</t>
+          <t>0; 6713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>342; 14414</t>
+          <t>3047; 24057</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>19243</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1881; 13182</t>
+          <t>1883; 12326</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1796; 10025</t>
+          <t>1784; 10318</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6780</t>
+          <t>0; 7631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4010; 20951</t>
+          <t>5208; 28086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1885; 10823</t>
+          <t>1934; 11361</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7541; 24119</t>
+          <t>7620; 24670</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1653; 9872</t>
+          <t>1708; 10254</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1840; 11078</t>
+          <t>2188; 12911</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5410; 18620</t>
+          <t>5354; 19307</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11190; 30216</t>
+          <t>11313; 31150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2901; 13290</t>
+          <t>2757; 13656</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8218; 28767</t>
+          <t>10289; 36018</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>17303</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1028; 13813</t>
+          <t>1656; 12898</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2929; 16461</t>
+          <t>2638; 15805</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1932; 12585</t>
+          <t>1907; 12325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2804; 14831</t>
+          <t>2696; 14734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2178; 12920</t>
+          <t>2995; 13489</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5886; 20300</t>
+          <t>5946; 21427</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1859; 10385</t>
+          <t>1847; 10347</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3920; 13046</t>
+          <t>5753; 16558</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5669; 20606</t>
+          <t>6172; 21566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11395; 30905</t>
+          <t>10733; 29823</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4888; 17990</t>
+          <t>4865; 18159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8988; 24080</t>
+          <t>10947; 26349</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>36371</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2085; 12621</t>
+          <t>2083; 12772</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7512; 26384</t>
+          <t>7986; 25460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6432; 22658</t>
+          <t>6583; 21163</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5606; 27397</t>
+          <t>10268; 27970</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5138; 17770</t>
+          <t>5055; 17769</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8233; 24428</t>
+          <t>8396; 25057</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2035; 12869</t>
+          <t>2934; 13223</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10694; 23316</t>
+          <t>12356; 26245</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9422; 26498</t>
+          <t>10335; 26699</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19285; 44461</t>
+          <t>19706; 44724</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11025; 28819</t>
+          <t>11074; 28748</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19326; 45019</t>
+          <t>27177; 48147</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>46603</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7182; 21273</t>
+          <t>6988; 21061</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4070; 15815</t>
+          <t>3925; 14942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1939; 14876</t>
+          <t>1972; 15082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13614; 32032</t>
+          <t>14305; 34271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4181; 16256</t>
+          <t>4040; 15778</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6279; 19712</t>
+          <t>6075; 19650</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>966; 9228</t>
+          <t>966; 9117</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13811; 27010</t>
+          <t>16784; 31562</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13052; 31532</t>
+          <t>13486; 33293</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12852; 31121</t>
+          <t>12561; 30201</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4106; 19081</t>
+          <t>3927; 21444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30744; 54229</t>
+          <t>35574; 59134</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>222866</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>234915</t>
+          <t>34328</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7943; 21313</t>
+          <t>7329; 21330</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2018; 15078</t>
+          <t>1970; 14818</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>949; 10362</t>
+          <t>947; 11397</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7532; 19129</t>
+          <t>8690; 21776</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1896; 11073</t>
+          <t>1909; 11923</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5757; 19257</t>
+          <t>5899; 21014</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2035; 11375</t>
+          <t>2715; 13412</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24001; 429837</t>
+          <t>14292; 27541</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12531; 29102</t>
+          <t>12494; 28955</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10055; 27958</t>
+          <t>9862; 28332</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4780; 18217</t>
+          <t>4808; 17249</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33754; 579951</t>
+          <t>26199; 43911</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>45729</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1799; 11729</t>
+          <t>1768; 11479</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5065; 18061</t>
+          <t>5159; 18486</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>808; 9326</t>
+          <t>911; 10245</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5668; 16585</t>
+          <t>6363; 18093</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7819; 23551</t>
+          <t>7931; 24523</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6247; 19793</t>
+          <t>6102; 20229</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6007; 22520</t>
+          <t>5175; 22560</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23592; 39644</t>
+          <t>27178; 44764</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12050; 30249</t>
+          <t>12135; 31483</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13670; 32584</t>
+          <t>14198; 32352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9000; 28244</t>
+          <t>8887; 27392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32763; 51840</t>
+          <t>36126; 57941</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>307454</t>
+          <t>120685</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>384209</t>
+          <t>208690</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>37661; 66661</t>
+          <t>37702; 65606</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43454; 76525</t>
+          <t>42672; 75290</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22996; 48808</t>
+          <t>22904; 50111</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>58510; 99242</t>
+          <t>69106; 110224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43136; 72447</t>
+          <t>43055; 73542</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>62695; 97628</t>
+          <t>61273; 96951</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26546; 51329</t>
+          <t>26305; 51035</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>103528; 935404</t>
+          <t>102653; 141561</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>87814; 127417</t>
+          <t>87785; 127834</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>113441; 160581</t>
+          <t>112025; 162776</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56035; 93225</t>
+          <t>54381; 90609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>177115; 1053611</t>
+          <t>185026; 238607</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
